--- a/product-definitions/spreadsheet/ch4-co2-h2o-concentration.xlsx
+++ b/product-definitions/spreadsheet/ch4-co2-h2o-concentration.xlsx
@@ -240,7 +240,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -270,11 +270,6 @@
     <font>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -348,7 +343,7 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="top"/>
     </xf>
@@ -364,7 +359,7 @@
     <xf borderId="0" fillId="2" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
@@ -2065,7 +2060,7 @@
       <c r="Y20" s="8"/>
       <c r="Z20" s="8"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="8"/>
       <c r="B21" s="8" t="s">
         <v>19</v>
@@ -2097,7 +2092,7 @@
       <c r="Y21" s="8"/>
       <c r="Z21" s="8"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="8"/>
       <c r="B22" s="8" t="s">
         <v>20</v>
@@ -2129,7 +2124,7 @@
       <c r="Y22" s="8"/>
       <c r="Z22" s="8"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="8" t="s">
         <v>22</v>
@@ -2161,7 +2156,7 @@
       <c r="Y23" s="8"/>
       <c r="Z23" s="8"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="8" t="s">
         <v>23</v>
@@ -2193,7 +2188,7 @@
       <c r="Y24" s="8"/>
       <c r="Z24" s="8"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="8" t="s">
         <v>25</v>
@@ -2225,7 +2220,7 @@
       <c r="Y25" s="8"/>
       <c r="Z25" s="8"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="9" t="s">
         <v>26</v>
@@ -2257,7 +2252,7 @@
       <c r="Y26" s="8"/>
       <c r="Z26" s="8"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="8"/>
       <c r="B27" s="8" t="s">
         <v>28</v>
@@ -2289,7 +2284,7 @@
       <c r="Y27" s="8"/>
       <c r="Z27" s="8"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="8"/>
       <c r="B28" s="15" t="s">
         <v>30</v>
@@ -2321,7 +2316,7 @@
       <c r="Y28" s="8"/>
       <c r="Z28" s="8"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="6"/>
@@ -2329,7 +2324,7 @@
       <c r="E29" s="8"/>
       <c r="F29" s="8"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>35</v>
       </c>
@@ -2339,7 +2334,7 @@
       <c r="E30" s="8"/>
       <c r="F30" s="8"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="8"/>
       <c r="B31" s="8" t="s">
         <v>10</v>
@@ -2351,7 +2346,7 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="8"/>
       <c r="B32" s="8" t="s">
         <v>12</v>
@@ -2363,7 +2358,7 @@
       <c r="E32" s="8"/>
       <c r="F32" s="8"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="9" t="s">
         <v>2</v>
@@ -2375,7 +2370,7 @@
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="8"/>
       <c r="B34" s="8" t="s">
         <v>19</v>
@@ -2387,7 +2382,7 @@
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="8"/>
       <c r="B35" s="8" t="s">
         <v>20</v>
@@ -2399,7 +2394,7 @@
       <c r="E35" s="8"/>
       <c r="F35" s="8"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="8"/>
       <c r="B36" s="8" t="s">
         <v>22</v>
@@ -2411,7 +2406,7 @@
       <c r="E36" s="8"/>
       <c r="F36" s="8"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="8"/>
       <c r="B37" s="8" t="s">
         <v>23</v>
@@ -2423,7 +2418,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="8"/>
       <c r="B38" s="8" t="s">
         <v>25</v>
@@ -2435,7 +2430,7 @@
       <c r="E38" s="8"/>
       <c r="F38" s="8"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="8"/>
       <c r="B39" s="9" t="s">
         <v>26</v>
@@ -2447,7 +2442,7 @@
       </c>
       <c r="F39" s="8"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="8"/>
       <c r="B40" s="8" t="s">
         <v>28</v>
@@ -2459,7 +2454,7 @@
       <c r="E40" s="8"/>
       <c r="F40" s="8"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="8"/>
       <c r="B41" s="15" t="s">
         <v>30</v>
@@ -2471,7 +2466,7 @@
       <c r="E41" s="8"/>
       <c r="F41" s="8"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -2479,7 +2474,7 @@
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="7" t="s">
         <v>38</v>
       </c>
@@ -2489,7 +2484,7 @@
       <c r="E43" s="8"/>
       <c r="F43" s="8"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="8"/>
       <c r="B44" s="8" t="s">
         <v>10</v>
@@ -2501,7 +2496,7 @@
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="8"/>
       <c r="B45" s="8" t="s">
         <v>12</v>
@@ -2513,7 +2508,7 @@
       <c r="E45" s="8"/>
       <c r="F45" s="8"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="9"/>
       <c r="B46" s="9" t="s">
         <v>2</v>
@@ -2525,7 +2520,7 @@
       <c r="E46" s="6"/>
       <c r="F46" s="8"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="8"/>
       <c r="B47" s="8" t="s">
         <v>19</v>
@@ -2537,7 +2532,7 @@
       <c r="E47" s="8"/>
       <c r="F47" s="8"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="8"/>
       <c r="B48" s="8" t="s">
         <v>20</v>
@@ -2549,7 +2544,7 @@
       <c r="E48" s="8"/>
       <c r="F48" s="8"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="8"/>
       <c r="B49" s="8" t="s">
         <v>22</v>
@@ -2561,7 +2556,7 @@
       <c r="E49" s="8"/>
       <c r="F49" s="8"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="8"/>
       <c r="B50" s="8" t="s">
         <v>23</v>
@@ -2573,7 +2568,7 @@
       <c r="E50" s="8"/>
       <c r="F50" s="8"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="8"/>
       <c r="B51" s="8" t="s">
         <v>25</v>
@@ -2585,7 +2580,7 @@
       <c r="E51" s="8"/>
       <c r="F51" s="8"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="8"/>
       <c r="B52" s="9" t="s">
         <v>26</v>
@@ -2597,7 +2592,7 @@
       </c>
       <c r="F52" s="8"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="8"/>
       <c r="B53" s="8" t="s">
         <v>28</v>
@@ -2609,7 +2604,7 @@
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="8"/>
       <c r="B54" s="15" t="s">
         <v>30</v>
@@ -2621,7 +2616,7 @@
       <c r="E54" s="8"/>
       <c r="F54" s="8"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="7"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -2629,12 +2624,12 @@
       <c r="E55" s="8"/>
       <c r="F55" s="8"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="19"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="7" t="s">
         <v>41</v>
       </c>
@@ -2644,7 +2639,7 @@
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="8"/>
       <c r="B58" s="8" t="s">
         <v>10</v>
@@ -2656,7 +2651,7 @@
       <c r="E58" s="8"/>
       <c r="F58" s="8"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="8"/>
       <c r="B59" s="8" t="s">
         <v>12</v>
@@ -2668,7 +2663,7 @@
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="9"/>
       <c r="B60" s="9" t="s">
         <v>2</v>
@@ -2682,7 +2677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="8"/>
       <c r="B61" s="9" t="s">
         <v>16</v>
@@ -2696,7 +2691,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="8"/>
       <c r="B62" s="8" t="s">
         <v>19</v>
@@ -2708,7 +2703,7 @@
       <c r="E62" s="8"/>
       <c r="F62" s="8"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="8"/>
       <c r="B63" s="8" t="s">
         <v>20</v>
@@ -2720,7 +2715,7 @@
       <c r="E63" s="8"/>
       <c r="F63" s="8"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="8"/>
       <c r="B64" s="8" t="s">
         <v>22</v>
@@ -2732,7 +2727,7 @@
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="8"/>
       <c r="B65" s="8" t="s">
         <v>23</v>
@@ -2744,7 +2739,7 @@
       <c r="E65" s="8"/>
       <c r="F65" s="8"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="8"/>
       <c r="B66" s="8" t="s">
         <v>25</v>
@@ -2756,7 +2751,7 @@
       <c r="E66" s="8"/>
       <c r="F66" s="8"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="8"/>
       <c r="B67" s="9" t="s">
         <v>26</v>
@@ -2768,7 +2763,7 @@
       </c>
       <c r="F67" s="8"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="8"/>
       <c r="B68" s="8" t="s">
         <v>28</v>
@@ -2780,7 +2775,7 @@
       <c r="E68" s="8"/>
       <c r="F68" s="8"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="8"/>
       <c r="B69" s="15" t="s">
         <v>30</v>
@@ -2792,12 +2787,12 @@
       <c r="E69" s="8"/>
       <c r="F69" s="8"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="16"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="7" t="s">
         <v>44</v>
       </c>
@@ -2807,7 +2802,7 @@
       <c r="E71" s="8"/>
       <c r="F71" s="8"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="8"/>
       <c r="B72" s="8" t="s">
         <v>10</v>
@@ -2819,7 +2814,7 @@
       <c r="E72" s="8"/>
       <c r="F72" s="8"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="8"/>
       <c r="B73" s="8" t="s">
         <v>12</v>
@@ -2831,7 +2826,7 @@
       <c r="E73" s="8"/>
       <c r="F73" s="8"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="9"/>
       <c r="B74" s="9" t="s">
         <v>2</v>
@@ -2845,7 +2840,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="8"/>
       <c r="B75" s="9" t="s">
         <v>16</v>
@@ -2859,7 +2854,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="8"/>
       <c r="B76" s="8" t="s">
         <v>19</v>
@@ -2871,7 +2866,7 @@
       <c r="E76" s="8"/>
       <c r="F76" s="8"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="8"/>
       <c r="B77" s="8" t="s">
         <v>20</v>
@@ -2883,7 +2878,7 @@
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="8"/>
       <c r="B78" s="8" t="s">
         <v>22</v>
@@ -2895,7 +2890,7 @@
       <c r="E78" s="8"/>
       <c r="F78" s="8"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="8"/>
       <c r="B79" s="8" t="s">
         <v>23</v>
@@ -2907,7 +2902,7 @@
       <c r="E79" s="8"/>
       <c r="F79" s="8"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="8"/>
       <c r="B80" s="8" t="s">
         <v>25</v>
@@ -2919,7 +2914,7 @@
       <c r="E80" s="8"/>
       <c r="F80" s="8"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="8"/>
       <c r="B81" s="9" t="s">
         <v>26</v>
@@ -2931,7 +2926,7 @@
       </c>
       <c r="F81" s="8"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="8"/>
       <c r="B82" s="8" t="s">
         <v>28</v>
@@ -2943,7 +2938,7 @@
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="8"/>
       <c r="B83" s="15" t="s">
         <v>30</v>
@@ -2955,7 +2950,7 @@
       <c r="E83" s="8"/>
       <c r="F83" s="8"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="8"/>
       <c r="B84" s="8"/>
       <c r="C84" s="6"/>
@@ -2963,7 +2958,7 @@
       <c r="E84" s="8"/>
       <c r="F84" s="8"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="7" t="s">
         <v>46</v>
       </c>
@@ -2973,7 +2968,7 @@
       <c r="E85" s="8"/>
       <c r="F85" s="8"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="8"/>
       <c r="B86" s="8" t="s">
         <v>10</v>
@@ -2985,7 +2980,7 @@
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="8"/>
       <c r="B87" s="8" t="s">
         <v>12</v>
@@ -2997,7 +2992,7 @@
       <c r="E87" s="8"/>
       <c r="F87" s="8"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="9"/>
       <c r="B88" s="9" t="s">
         <v>2</v>
@@ -3009,7 +3004,7 @@
       <c r="E88" s="6"/>
       <c r="F88" s="6"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="8"/>
       <c r="B89" s="8" t="s">
         <v>19</v>
@@ -3021,7 +3016,7 @@
       <c r="E89" s="8"/>
       <c r="F89" s="8"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="8"/>
       <c r="B90" s="8" t="s">
         <v>20</v>
@@ -3033,7 +3028,7 @@
       <c r="E90" s="8"/>
       <c r="F90" s="8"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="8"/>
       <c r="B91" s="8" t="s">
         <v>22</v>
@@ -3045,7 +3040,7 @@
       <c r="E91" s="8"/>
       <c r="F91" s="8"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="8"/>
       <c r="B92" s="8" t="s">
         <v>23</v>
@@ -3057,7 +3052,7 @@
       <c r="E92" s="8"/>
       <c r="F92" s="8"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="8"/>
       <c r="B93" s="8" t="s">
         <v>25</v>
@@ -3069,7 +3064,7 @@
       <c r="E93" s="8"/>
       <c r="F93" s="8"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="8"/>
       <c r="B94" s="9" t="s">
         <v>26</v>
@@ -3081,7 +3076,7 @@
       </c>
       <c r="F94" s="8"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="8"/>
       <c r="B95" s="8" t="s">
         <v>28</v>
@@ -3093,7 +3088,7 @@
       <c r="E95" s="8"/>
       <c r="F95" s="8"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="8"/>
       <c r="B96" s="15" t="s">
         <v>30</v>
@@ -3105,10 +3100,10 @@
       <c r="E96" s="8"/>
       <c r="F96" s="8"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="C97" s="20"/>
     </row>
-    <row r="98">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="7" t="s">
         <v>48</v>
       </c>
@@ -3118,7 +3113,7 @@
       <c r="E98" s="8"/>
       <c r="F98" s="8"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="8"/>
       <c r="B99" s="8" t="s">
         <v>10</v>
@@ -3130,7 +3125,7 @@
       <c r="E99" s="8"/>
       <c r="F99" s="8"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="8"/>
       <c r="B100" s="8" t="s">
         <v>12</v>
@@ -3142,7 +3137,7 @@
       <c r="E100" s="8"/>
       <c r="F100" s="8"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="9"/>
       <c r="B101" s="9" t="s">
         <v>2</v>
@@ -3154,7 +3149,7 @@
       <c r="E101" s="6"/>
       <c r="F101" s="8"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="8"/>
       <c r="B102" s="8" t="s">
         <v>19</v>
@@ -3166,7 +3161,7 @@
       <c r="E102" s="8"/>
       <c r="F102" s="8"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="8"/>
       <c r="B103" s="8" t="s">
         <v>20</v>
@@ -3178,7 +3173,7 @@
       <c r="E103" s="8"/>
       <c r="F103" s="8"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="8"/>
       <c r="B104" s="8" t="s">
         <v>22</v>
@@ -3190,7 +3185,7 @@
       <c r="E104" s="8"/>
       <c r="F104" s="8"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="8"/>
       <c r="B105" s="8" t="s">
         <v>23</v>
@@ -3202,7 +3197,7 @@
       <c r="E105" s="8"/>
       <c r="F105" s="8"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="8"/>
       <c r="B106" s="8" t="s">
         <v>25</v>
@@ -3214,7 +3209,7 @@
       <c r="E106" s="8"/>
       <c r="F106" s="8"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="8"/>
       <c r="B107" s="9" t="s">
         <v>26</v>
@@ -3226,7 +3221,7 @@
       </c>
       <c r="F107" s="8"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="8"/>
       <c r="B108" s="8" t="s">
         <v>28</v>
@@ -3238,7 +3233,7 @@
       <c r="E108" s="8"/>
       <c r="F108" s="8"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="8"/>
       <c r="B109" s="15" t="s">
         <v>30</v>
@@ -3250,10 +3245,10 @@
       <c r="E109" s="8"/>
       <c r="F109" s="8"/>
     </row>
-    <row r="110">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="C110" s="20"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="7" t="s">
         <v>50</v>
       </c>
@@ -3263,7 +3258,7 @@
       <c r="E111" s="8"/>
       <c r="F111" s="8"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="8"/>
       <c r="B112" s="8" t="s">
         <v>10</v>
@@ -3275,7 +3270,7 @@
       <c r="E112" s="8"/>
       <c r="F112" s="8"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="8"/>
       <c r="B113" s="8" t="s">
         <v>12</v>
@@ -3287,7 +3282,7 @@
       <c r="E113" s="8"/>
       <c r="F113" s="8"/>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="9"/>
       <c r="B114" s="9" t="s">
         <v>2</v>
@@ -3301,7 +3296,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="8"/>
       <c r="B115" s="9" t="s">
         <v>16</v>
@@ -3315,7 +3310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="8"/>
       <c r="B116" s="8" t="s">
         <v>19</v>
@@ -3327,7 +3322,7 @@
       <c r="E116" s="8"/>
       <c r="F116" s="8"/>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="8"/>
       <c r="B117" s="8" t="s">
         <v>20</v>
@@ -3339,7 +3334,7 @@
       <c r="E117" s="8"/>
       <c r="F117" s="8"/>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="8"/>
       <c r="B118" s="8" t="s">
         <v>22</v>
@@ -3351,7 +3346,7 @@
       <c r="E118" s="8"/>
       <c r="F118" s="8"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="8"/>
       <c r="B119" s="8" t="s">
         <v>23</v>
@@ -3363,7 +3358,7 @@
       <c r="E119" s="8"/>
       <c r="F119" s="8"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="8"/>
       <c r="B120" s="8" t="s">
         <v>25</v>
@@ -3375,7 +3370,7 @@
       <c r="E120" s="8"/>
       <c r="F120" s="8"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="8"/>
       <c r="B121" s="9" t="s">
         <v>26</v>
@@ -3387,7 +3382,7 @@
       </c>
       <c r="F121" s="8"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="8"/>
       <c r="B122" s="8" t="s">
         <v>28</v>
@@ -3399,7 +3394,7 @@
       <c r="E122" s="8"/>
       <c r="F122" s="8"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="8"/>
       <c r="B123" s="15" t="s">
         <v>30</v>
@@ -3411,12 +3406,12 @@
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="16"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="7" t="s">
         <v>53</v>
       </c>
@@ -3426,7 +3421,7 @@
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="8"/>
       <c r="B126" s="8" t="s">
         <v>10</v>
@@ -3438,7 +3433,7 @@
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="8"/>
       <c r="B127" s="8" t="s">
         <v>12</v>
@@ -3450,7 +3445,7 @@
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="9"/>
       <c r="B128" s="9" t="s">
         <v>2</v>
@@ -3464,7 +3459,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="8"/>
       <c r="B129" s="9" t="s">
         <v>16</v>
@@ -3478,7 +3473,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="8"/>
       <c r="B130" s="8" t="s">
         <v>19</v>
@@ -3490,7 +3485,7 @@
       </c>
       <c r="F130" s="8"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="8"/>
       <c r="B131" s="8" t="s">
         <v>20</v>
@@ -3502,7 +3497,7 @@
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="8"/>
       <c r="B132" s="8" t="s">
         <v>22</v>
@@ -3514,7 +3509,7 @@
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="8"/>
       <c r="B133" s="8" t="s">
         <v>23</v>
@@ -3526,7 +3521,7 @@
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="8"/>
       <c r="B134" s="8" t="s">
         <v>25</v>
@@ -3538,7 +3533,7 @@
       <c r="E134" s="8"/>
       <c r="F134" s="8"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="8"/>
       <c r="B135" s="9" t="s">
         <v>26</v>
@@ -3550,7 +3545,7 @@
       </c>
       <c r="F135" s="8"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="8"/>
       <c r="B136" s="8" t="s">
         <v>28</v>
@@ -3562,7 +3557,7 @@
       <c r="E136" s="8"/>
       <c r="F136" s="8"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="8"/>
       <c r="B137" s="15" t="s">
         <v>30</v>
@@ -3574,7 +3569,7 @@
       <c r="E137" s="8"/>
       <c r="F137" s="8"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="8"/>
       <c r="B138" s="8"/>
       <c r="C138" s="6"/>
@@ -3582,7 +3577,7 @@
       <c r="E138" s="8"/>
       <c r="F138" s="8"/>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="7" t="s">
         <v>55</v>
       </c>
@@ -3592,7 +3587,7 @@
       <c r="E139" s="8"/>
       <c r="F139" s="8"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="8"/>
       <c r="B140" s="8" t="s">
         <v>10</v>
@@ -3604,7 +3599,7 @@
       <c r="E140" s="8"/>
       <c r="F140" s="8"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="8"/>
       <c r="B141" s="8" t="s">
         <v>12</v>
@@ -3616,7 +3611,7 @@
       <c r="E141" s="8"/>
       <c r="F141" s="8"/>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="9"/>
       <c r="B142" s="9" t="s">
         <v>2</v>
@@ -3628,7 +3623,7 @@
       <c r="E142" s="6"/>
       <c r="F142" s="6"/>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="8"/>
       <c r="B143" s="8" t="s">
         <v>19</v>
@@ -3640,7 +3635,7 @@
       <c r="E143" s="8"/>
       <c r="F143" s="8"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="8"/>
       <c r="B144" s="8" t="s">
         <v>20</v>
@@ -3652,7 +3647,7 @@
       <c r="E144" s="8"/>
       <c r="F144" s="8"/>
     </row>
-    <row r="145">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="8"/>
       <c r="B145" s="8" t="s">
         <v>22</v>
@@ -3664,7 +3659,7 @@
       <c r="E145" s="8"/>
       <c r="F145" s="8"/>
     </row>
-    <row r="146">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="8"/>
       <c r="B146" s="8" t="s">
         <v>23</v>
@@ -3676,7 +3671,7 @@
       <c r="E146" s="8"/>
       <c r="F146" s="8"/>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="8"/>
       <c r="B147" s="8" t="s">
         <v>25</v>
@@ -3688,7 +3683,7 @@
       <c r="E147" s="8"/>
       <c r="F147" s="8"/>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="8"/>
       <c r="B148" s="9" t="s">
         <v>26</v>
@@ -3700,7 +3695,7 @@
       </c>
       <c r="F148" s="8"/>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="8"/>
       <c r="B149" s="8" t="s">
         <v>28</v>
@@ -3712,7 +3707,7 @@
       <c r="E149" s="8"/>
       <c r="F149" s="8"/>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="8"/>
       <c r="B150" s="15" t="s">
         <v>30</v>
@@ -3724,10 +3719,10 @@
       <c r="E150" s="8"/>
       <c r="F150" s="8"/>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="C151" s="20"/>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="7" t="s">
         <v>57</v>
       </c>
@@ -3737,7 +3732,7 @@
       <c r="E152" s="8"/>
       <c r="F152" s="8"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="8"/>
       <c r="B153" s="8" t="s">
         <v>10</v>
@@ -3749,7 +3744,7 @@
       <c r="E153" s="8"/>
       <c r="F153" s="8"/>
     </row>
-    <row r="154">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="8"/>
       <c r="B154" s="8" t="s">
         <v>12</v>
@@ -3761,7 +3756,7 @@
       <c r="E154" s="8"/>
       <c r="F154" s="8"/>
     </row>
-    <row r="155">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="9"/>
       <c r="B155" s="9" t="s">
         <v>2</v>
@@ -3773,7 +3768,7 @@
       <c r="E155" s="6"/>
       <c r="F155" s="8"/>
     </row>
-    <row r="156">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="8"/>
       <c r="B156" s="8" t="s">
         <v>19</v>
@@ -3785,7 +3780,7 @@
       <c r="E156" s="8"/>
       <c r="F156" s="8"/>
     </row>
-    <row r="157">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="8"/>
       <c r="B157" s="8" t="s">
         <v>20</v>
@@ -3797,7 +3792,7 @@
       <c r="E157" s="8"/>
       <c r="F157" s="8"/>
     </row>
-    <row r="158">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="8"/>
       <c r="B158" s="8" t="s">
         <v>22</v>
@@ -3809,7 +3804,7 @@
       <c r="E158" s="8"/>
       <c r="F158" s="8"/>
     </row>
-    <row r="159">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="8"/>
       <c r="B159" s="8" t="s">
         <v>23</v>
@@ -3821,7 +3816,7 @@
       <c r="E159" s="8"/>
       <c r="F159" s="8"/>
     </row>
-    <row r="160">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="8"/>
       <c r="B160" s="8" t="s">
         <v>25</v>
@@ -3833,7 +3828,7 @@
       <c r="E160" s="8"/>
       <c r="F160" s="8"/>
     </row>
-    <row r="161">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="8"/>
       <c r="B161" s="9" t="s">
         <v>26</v>
@@ -3845,7 +3840,7 @@
       </c>
       <c r="F161" s="8"/>
     </row>
-    <row r="162">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="8"/>
       <c r="B162" s="8" t="s">
         <v>28</v>
@@ -3857,7 +3852,7 @@
       <c r="E162" s="8"/>
       <c r="F162" s="8"/>
     </row>
-    <row r="163">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="8"/>
       <c r="B163" s="15" t="s">
         <v>30</v>
@@ -3869,17 +3864,17 @@
       <c r="E163" s="8"/>
       <c r="F163" s="8"/>
     </row>
-    <row r="164">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="C164" s="20"/>
     </row>
-    <row r="165">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="15" t="s">
         <v>59</v>
       </c>
       <c r="B165" s="15"/>
       <c r="C165" s="6"/>
     </row>
-    <row r="166">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="15"/>
       <c r="B166" s="15" t="s">
         <v>10</v>
@@ -3888,7 +3883,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="15"/>
       <c r="B167" s="15" t="s">
         <v>12</v>
@@ -3897,7 +3892,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="15"/>
       <c r="B168" s="15" t="s">
         <v>2</v>
@@ -3908,7 +3903,7 @@
       <c r="D168" s="6"/>
       <c r="E168" s="6"/>
     </row>
-    <row r="169">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="15"/>
       <c r="B169" s="15" t="s">
         <v>19</v>
@@ -3917,7 +3912,7 @@
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
     </row>
-    <row r="170">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="15"/>
       <c r="B170" s="15" t="s">
         <v>20</v>
@@ -3926,7 +3921,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="15"/>
       <c r="B171" s="8" t="s">
         <v>62</v>
@@ -3935,7 +3930,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="15"/>
       <c r="B172" s="6" t="s">
         <v>64</v>
@@ -3944,19 +3939,19 @@
         <v>65</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="24"/>
     </row>
-    <row r="174">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="16" t="s">
         <v>66</v>
       </c>
       <c r="B174" s="2"/>
       <c r="C174" s="19"/>
     </row>
-    <row r="175">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="2"/>
       <c r="B175" s="2" t="s">
         <v>10</v>
@@ -3965,7 +3960,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="2"/>
       <c r="B176" s="2" t="s">
         <v>12</v>
@@ -3974,7 +3969,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="2"/>
       <c r="B177" s="2" t="s">
         <v>2</v>
@@ -3983,14 +3978,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="2"/>
       <c r="B178" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C178" s="25"/>
     </row>
-    <row r="179">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="2"/>
       <c r="B179" s="2" t="s">
         <v>20</v>
@@ -3999,7 +3994,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="2"/>
       <c r="B180" s="8" t="s">
         <v>62</v>
@@ -4008,7 +4003,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="2"/>
       <c r="B181" s="6" t="s">
         <v>64</v>
@@ -4017,19 +4012,19 @@
         <v>65</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="19"/>
     </row>
-    <row r="183">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="16" t="s">
         <v>68</v>
       </c>
       <c r="B183" s="2"/>
       <c r="C183" s="19"/>
     </row>
-    <row r="184">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="2"/>
       <c r="B184" s="2" t="s">
         <v>10</v>
@@ -4038,7 +4033,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="2"/>
       <c r="B185" s="2" t="s">
         <v>12</v>
@@ -4047,7 +4042,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="2"/>
       <c r="B186" s="2" t="s">
         <v>2</v>
@@ -4056,14 +4051,14 @@
         <v>1.0</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="2"/>
       <c r="B187" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C187" s="25"/>
     </row>
-    <row r="188">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="2"/>
       <c r="B188" s="2" t="s">
         <v>20</v>
@@ -4072,7 +4067,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="2"/>
       <c r="B189" s="8" t="s">
         <v>62</v>
@@ -4081,7 +4076,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="2"/>
       <c r="B190" s="6" t="s">
         <v>64</v>
